--- a/Data/Cglutanicum_phenotypes/cglutanicum_proteomics.xlsx
+++ b/Data/Cglutanicum_phenotypes/cglutanicum_proteomics.xlsx
@@ -5,13 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="ribosome_fraction" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="proteome_fraction" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="proteome_fraction" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t xml:space="preserve">ribosome_fraction</t>
   </si>
@@ -125,42 +124,6 @@
   </si>
   <si>
     <t xml:space="preserve">CGXII+Glutamate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">substrate uptake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://journals.asm.org/doi/epdf/10.1128/aem.62.2.429-436.1996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCAIGN-BOUSQUET ET AL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">co2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glc_upt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02+0.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mu</t>
   </si>
   <si>
     <t xml:space="preserve">condition</t>
@@ -248,11 +211,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -274,6 +238,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -291,17 +256,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFBCBEC4"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -312,6 +266,7 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -396,7 +351,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -442,7 +397,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -453,31 +412,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,66 +437,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBCBEC4"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -559,7 +446,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:D15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.31"/>
@@ -688,13 +575,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="32.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="32.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -900,262 +787,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>0.933333333333333</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>0.21125</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>2.16666666666667</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>0.33375</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>3.53333333333333</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>0.3525</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>3.93333333333333</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>4.53333333333333</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>0.55625</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>2.42307692307692</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>0.215189873417721</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>5.01923076923077</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>0.336708860759494</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>7.73076923076923</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>0.358227848101266</v>
-      </c>
-      <c r="B15" s="0" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>0.449367088607595</v>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>9.34615384615385</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>0.563291139240506</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>9.63461538461539</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>0.60379746835443</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <v>6.23076923076923</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22" s="0" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>2.19354838709677</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
-        <v>0.214102564102564</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>4.83870967741936</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
-        <v>0.341025641025641</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>7.61290322580645</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
-        <v>0.358974358974359</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>9.03225806451613</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
-        <v>0.453846153846154</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>9.35483870967742</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
-        <v>0.567948717948718</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>9.41935483870968</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
-        <v>0.608974358974359</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>5.80645161290323</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.01"/>
@@ -1166,396 +799,396 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>0.715246506426215</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>0.294947012959264</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>0.470757675664931</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>0.0384491735536408</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>1.40953873957395</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>2.9375</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0.47984297517411</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>0.365736533423192</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>0.0134325613236185</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>2.04926492918554</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.504434444107209</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.420189964030125</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.0163850026788574</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>0.968194707499492</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.624641746773866</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.450024769223445</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.0632946257306561</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0.235622857257577</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0.6625</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.355657143030305</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.258879465654825</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.114235886180381</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.35110098006847</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.573226089907706</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.243609515319739</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.0110230956317055</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>0.715246506426215</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>0.294947012959264</v>
-      </c>
-      <c r="F2" s="18" t="n">
-        <v>0.470757675664931</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>0.0384491735536408</v>
-      </c>
-      <c r="H2" s="18" t="s">
+      <c r="B8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.690450562609517</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.712723161403373</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.173229172495265</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.0124079726935989</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="17" t="n">
-        <v>1.40953873957395</v>
-      </c>
-      <c r="D3" s="17" t="n">
-        <v>2.9375</v>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>0.47984297517411</v>
-      </c>
-      <c r="F3" s="18" t="n">
-        <v>0.365736533423192</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>0.0134325613236185</v>
-      </c>
-      <c r="H3" s="18" t="s">
+      <c r="B9" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.828393589234923</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.466700613653478</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.336232511499007</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.0107675296721047</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>2.04926492918554</v>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>4.0625</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>0.504434444107209</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <v>0.420189964030125</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>0.0163850026788574</v>
-      </c>
-      <c r="H4" s="18" t="s">
+      <c r="B10" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0.666593914200785</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>1.39375</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.47827366041312</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.247492055937684</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.00686282633173989</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>0.968194707499492</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>0.624641746773866</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.450024769223445</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.0632946257306561</v>
-      </c>
-      <c r="H5" s="18" t="s">
+      <c r="B11" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0.690450562609517</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>1.34375</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.513823674500106</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.32689650039662</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.00635635559936308</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>0.235622857257577</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>0.6625</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.355657143030305</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.258879465654825</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.114235886180381</v>
-      </c>
-      <c r="H6" s="18" t="s">
+      <c r="B12" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.745540659804752</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.608604620248777</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.336680830187841</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.0167926431877032</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>0.35110098006847</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>0.6125</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0.573226089907706</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.243609515319739</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.0110230956317055</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="B13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0.232868302648487</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.517485116996638</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.188024950357255</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.00965871067191694</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0.690450562609517</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0.96875</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.712723161403373</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0.173229172495265</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.0124079726935989</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <v>0.828393589234923</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0.466700613653478</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.336232511499007</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0107675296721047</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0.666593914200785</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>1.39375</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.47827366041312</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.247492055937684</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.00686282633173989</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>0.690450562609517</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>1.34375</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.513823674500106</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.32689650039662</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.00635635559936308</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0.745540659804752</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.608604620248777</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0.336680830187841</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.0167926431877032</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>0.232868302648487</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.517485116996638</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>0.188024950357255</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.00965871067191694</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
